--- a/data/KrÃ³nan_Master_SkrÃ¡.xlsx
+++ b/data/KrÃ³nan_Master_SkrÃ¡.xlsx
@@ -20,8 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +39,12 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +61,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00117A65"/>
         <bgColor rgb="00117A65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF5FB"/>
+        <bgColor rgb="00EBF5FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E8449"/>
+        <bgColor rgb="001E8449"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A5276"/>
+        <bgColor rgb="001A5276"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E9F7EF"/>
+        <bgColor rgb="00E9F7EF"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,12 +120,81 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -455,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -498,6 +605,438 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>73198.08279999999</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>0.1114032860734006</v>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Flatahrauni</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="n">
+        <v>72977.4074</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>97</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <v>0.1110674307644203</v>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Granda</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>68031.39279999999</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>103</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>0.1035398800645949</v>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Lindum</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>66432.3026</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>95</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0.1011061564451592</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Bíldshöfða</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>60982.8462</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>0.09281239618462785</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Mosfellsbæ</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>56644.04320000001</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>82</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>0.08620898673269166</v>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Fitjabraut</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>38247.72000000001</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>0.05821083735837038</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Vallakór</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>35572.0111</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0.05413856179276165</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Hallveigarstíg</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>31549.51</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>0.04801654570118897</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Akrabraut</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>23887.35</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0.03635517740070437</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Norðurhellu</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>22639.62</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>0.03445620386457831</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Akranesi</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>21810.8024</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>0.03319479098785376</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Borgartún</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>20837.8029</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0.03171394152429684</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Austurveri</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>19540.5271</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>0.02973956212069448</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Jafnaseli</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>17757.65</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>0.02702612537471163</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Selfossi</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>13495.47</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>0.02053933173650001</v>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Grafarholti</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>10828.8116</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>0.0164808305130877</v>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Árbæ</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>2621.62</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>0.003989955360357452</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -509,7 +1048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -546,7 +1085,418 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="n">
+        <v>73198.08279999999</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>96</v>
+      </c>
+      <c r="E3" s="14" t="n">
+        <v>0.1114032860734006</v>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Flatahrauni</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>72977.4074</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.1110674307644203</v>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Granda</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>68031.39279999999</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>103</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>0.1035398800645949</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Lindum</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>66432.3026</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0.1011061564451592</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Bíldshöfða</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>60982.8462</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>0.09281239618462783</v>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Mosfellsbæ</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>56644.04320000001</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0.08620898673269164</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Fitjabraut</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>38247.72000000001</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0.05821083735837037</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Vallakór</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>35572.0111</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0.05413856179276164</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Hallveigarstíg</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>31549.51</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>0.04801654570118896</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Akrabraut</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>23887.35</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0.03635517740070436</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Norðurhellu</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>22639.62</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>0.0344562038645783</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Akranesi</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>21810.8024</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0.03319479098785376</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Borgartún</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>20837.8029</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>0.03171394152429683</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Austurveri</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>19540.5271</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>0.02973956212069447</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Jafnaseli</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>17757.65</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>0.02702612537471163</v>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Selfossi</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>13495.47</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>0.02053933173650001</v>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Grafarholti</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>10828.8116</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>0.01648083051308769</v>
+      </c>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Árbæ</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>2621.62</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>0.003989955360357451</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>HEILD 2026-06</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="n">
+        <v>657054.9701</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>751</v>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -557,7 +1507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -600,6 +1550,1134 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri lax teriya</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>98680.00279999999</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>159</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>0.150185307608253</v>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri kjúklingas</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="n">
+        <v>82918.75410000001</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>134</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <v>0.1261975905720343</v>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sterkur tú</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>70675.54440000001</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>114</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>0.107564127228569</v>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sulimi sal</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>43418.8201</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0.06608095528657504</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi vegan gyoza-ramen </t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>33864.8626</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>0.05154037963497325</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki soba núðlur m</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>31567.5429</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>0.04804399074128547</v>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi rjóma-ramen með sv</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>28945.91</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>0.04405401574786749</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki udon núðlur m</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>27621.5929</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0.04203848103575893</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklinga katsu po</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>19190.0782</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>0.02920619898374618</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir ch</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>17927.9</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0.02728523611543716</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi gyoza kjúklinga 6s</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>17783.7942</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>0.02706591534844247</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir so</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>16135.1154</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>0.0245567207223839</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi sushi lækkað verð </t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>16081.08</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0.02447448194106583</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi grillaður kjúkling</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>13621.6227</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>0.02073132891442381</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi laxafantasía 12bit</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>11783.7539</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>0.01793419795334108</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi kóreskir vængir 6 </t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>11554.03</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>0.0175845713460497</v>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi soba núðlusalat me</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>10459.45</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>0.01591868333087585</v>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi grillaður lax &amp; so</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>9864.860000000001</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>0.0150137514346762</v>
+      </c>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kóreskir chilivæng</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>8986.440000000001</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>0.01367684654851985</v>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingur &amp; sætnú</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>7891.889999999999</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>0.01201100419162631</v>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi 11 Ekkert hrátt 14</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>7864.86</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>0.01196986608107235</v>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingakatsu 8bi</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>7135.12</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>0.01085924363210292</v>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri vegan tófú</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>6806.29</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>0.01035878322169015</v>
+      </c>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi 13 Allt það besta </t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>6252.26</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>0.009515581320461576</v>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi eldfjallarúlla 6bi</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>5729.7299</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>0.008720320461358002</v>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi wakame salat</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>4945.950000000001</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>0.007527452382328461</v>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi Lítið laxatrío 10b</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>3927.92</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>0.005978069079063801</v>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi vegan eldfjallarúl</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>3918.93</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>0.00596438681439935</v>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi laxa nigiri 4 bita</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>3756.75</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>0.005717558151075616</v>
+      </c>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi Laxatrío 16bitar</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>3351.35</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>0.005100562589900117</v>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi laxatartar salat</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>2675.67</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>0.004072216362038595</v>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi rækju katsu karrí </t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>2423.43</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>0.003688321541242079</v>
+      </c>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi edamame með sjávar</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>2297.31</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>0.00349637413084382</v>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi Poke Laxakadó hrís</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>2144.16</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>0.003263288609891606</v>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi Poke veganbliss hr</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>2144.14</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>0.00326325817103807</v>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi 6. Smakk af því be</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>1927.93</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>0.002934198944886727</v>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi laxa og epla maki </t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>1738.74</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>0.002646262609862571</v>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi sojasósa</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>1625.186</v>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>0.002473439931141006</v>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi Rainbow maki 4bita</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>1441.44</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>0.002193789052049361</v>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi sterkt majó</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>1434.23</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>0.002182815845349619</v>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi gúrku sesam salat</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>1243.24</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>0.00189214001350722</v>
+      </c>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi 38 Avókadó hosomak</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>873.88</v>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>0.001329995266403662</v>
+      </c>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi mangó hosomaki 8bi</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>837.84</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>0.001275144452331721</v>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi agúrku hosomaki 8b</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>720.72</v>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>0.00109689452602468</v>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi súrsað engifer</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>576.5699999999999</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>0.0008775064891636833</v>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yuzu majónes</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>144.14</v>
+      </c>
+      <c r="E47" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>0.0002193728174342288</v>
+      </c>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi unagi sósa</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>144.14</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>0.0002193728174342288</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -611,7 +2689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -648,7 +2726,1027 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri lax teriya</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="n">
+        <v>98680.00279999999</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>159</v>
+      </c>
+      <c r="E3" s="14" t="n">
+        <v>0.150185307608253</v>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri kjúklingas</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="n">
+        <v>82918.75410000001</v>
+      </c>
+      <c r="D4" s="24" t="n">
+        <v>134</v>
+      </c>
+      <c r="E4" s="25" t="n">
+        <v>0.1261975905720343</v>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sterkur tú</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>70675.54440000001</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>114</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>0.107564127228569</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sulimi sal</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>43418.8201</v>
+      </c>
+      <c r="D6" s="24" t="n">
+        <v>70</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>0.06608095528657504</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi vegan gyoza-ramen </t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>33864.8626</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>0.05154037963497325</v>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki soba núðlur m</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>31567.5429</v>
+      </c>
+      <c r="D8" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>0.04804399074128547</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi rjóma-ramen með sv</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>28945.91</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>0.04405401574786749</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki udon núðlur m</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="n">
+        <v>27621.5929</v>
+      </c>
+      <c r="D10" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>0.04203848103575893</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklinga katsu po</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>19190.0782</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>0.02920619898374618</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir ch</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>17927.9</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>0.02728523611543716</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi gyoza kjúklinga 6s</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>17783.7942</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>0.02706591534844247</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir so</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="n">
+        <v>16135.1154</v>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>0.0245567207223839</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi sushi lækkað verð </t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>16081.08</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>0.02447448194106583</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi grillaður kjúkling</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="n">
+        <v>13621.6227</v>
+      </c>
+      <c r="D16" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>0.02073132891442381</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi laxafantasía 12bit</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>11783.7539</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>0.01793419795334108</v>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi kóreskir vængir 6 </t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="n">
+        <v>11554.03</v>
+      </c>
+      <c r="D18" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>0.0175845713460497</v>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi soba núðlusalat me</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>10459.45</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>0.01591868333087585</v>
+      </c>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi grillaður lax &amp; so</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="n">
+        <v>9864.860000000001</v>
+      </c>
+      <c r="D20" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="25" t="n">
+        <v>0.0150137514346762</v>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kóreskir chilivæng</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>8986.440000000001</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>0.01367684654851985</v>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingur &amp; sætnú</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="n">
+        <v>7891.889999999999</v>
+      </c>
+      <c r="D22" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" s="25" t="n">
+        <v>0.01201100419162631</v>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi 11 Ekkert hrátt 14</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>7864.86</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>0.01196986608107235</v>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingakatsu 8bi</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="n">
+        <v>7135.12</v>
+      </c>
+      <c r="D24" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="25" t="n">
+        <v>0.01085924363210292</v>
+      </c>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri vegan tófú</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>6806.29</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>0.01035878322169015</v>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi 13 Allt það besta </t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="n">
+        <v>6252.26</v>
+      </c>
+      <c r="D26" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="25" t="n">
+        <v>0.009515581320461576</v>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi eldfjallarúlla 6bi</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>5729.7299</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>0.008720320461358002</v>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi wakame salat</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="n">
+        <v>4945.950000000001</v>
+      </c>
+      <c r="D28" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" s="25" t="n">
+        <v>0.007527452382328461</v>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi Lítið laxatrío 10b</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>3927.92</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>0.005978069079063801</v>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi vegan eldfjallarúl</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="n">
+        <v>3918.93</v>
+      </c>
+      <c r="D30" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" s="25" t="n">
+        <v>0.00596438681439935</v>
+      </c>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi laxa nigiri 4 bita</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>3756.75</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>0.005717558151075616</v>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi Laxatrío 16bitar</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="n">
+        <v>3351.35</v>
+      </c>
+      <c r="D32" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>0.005100562589900117</v>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi laxatartar salat</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>2675.67</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>0.004072216362038595</v>
+      </c>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi rækju katsu karrí </t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="n">
+        <v>2423.43</v>
+      </c>
+      <c r="D34" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="25" t="n">
+        <v>0.003688321541242079</v>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi edamame með sjávar</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>2297.31</v>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>0.00349637413084382</v>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi Poke Laxakadó hrís</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="n">
+        <v>2144.16</v>
+      </c>
+      <c r="D36" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="25" t="n">
+        <v>0.003263288609891606</v>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi Poke veganbliss hr</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="n">
+        <v>2144.14</v>
+      </c>
+      <c r="D37" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>0.00326325817103807</v>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi 6. Smakk af því be</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="n">
+        <v>1927.93</v>
+      </c>
+      <c r="D38" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="25" t="n">
+        <v>0.002934198944886727</v>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi laxa og epla maki </t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>1738.74</v>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>0.002646262609862571</v>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi sojasósa</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="n">
+        <v>1625.186</v>
+      </c>
+      <c r="D40" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="E40" s="25" t="n">
+        <v>0.002473439931141006</v>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi Rainbow maki 4bita</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>1441.44</v>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>0.002193789052049361</v>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi sterkt majó</t>
+        </is>
+      </c>
+      <c r="C42" s="23" t="n">
+        <v>1434.23</v>
+      </c>
+      <c r="D42" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" s="25" t="n">
+        <v>0.002182815845349619</v>
+      </c>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi gúrku sesam salat</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>1243.24</v>
+      </c>
+      <c r="D43" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>0.00189214001350722</v>
+      </c>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi 38 Avókadó hosomak</t>
+        </is>
+      </c>
+      <c r="C44" s="23" t="n">
+        <v>873.88</v>
+      </c>
+      <c r="D44" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="25" t="n">
+        <v>0.001329995266403662</v>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi mangó hosomaki 8bi</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="n">
+        <v>837.84</v>
+      </c>
+      <c r="D45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>0.001275144452331721</v>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi agúrku hosomaki 8b</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="n">
+        <v>720.72</v>
+      </c>
+      <c r="D46" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="25" t="n">
+        <v>0.00109689452602468</v>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi súrsað engifer</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>576.5699999999999</v>
+      </c>
+      <c r="D47" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>0.0008775064891636833</v>
+      </c>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="21" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yuzu majónes</t>
+        </is>
+      </c>
+      <c r="C48" s="23" t="n">
+        <v>144.14</v>
+      </c>
+      <c r="D48" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="25" t="n">
+        <v>0.0002193728174342288</v>
+      </c>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi unagi sósa</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="n">
+        <v>144.14</v>
+      </c>
+      <c r="D49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>0.0002193728174342288</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>HEILD 2026-06</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>657054.9701</v>
+      </c>
+      <c r="D50" s="19" t="n">
+        <v>751</v>
+      </c>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -659,7 +3757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -702,6 +3800,6175 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Akrabraut</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sterkur tú</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>3108.11</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>100268875</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Akrabraut</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi kóreskir vængir 6 </t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>2567.56</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>100267488</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Akrabraut</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki soba núðlur m</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1972.97</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>100266622</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Akrabraut</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri kjúklingas</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>1864.86</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>100268871</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Akrabraut</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sulimi sal</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1864.86</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>100268877</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Akrabraut</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir ch</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>1792.79</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>100270213</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Akrabraut</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi rjóma-ramen með sv</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1702.7</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>100268876</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Akrabraut</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi vegan gyoza-ramen </t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>1612.61</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>100268873</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Akrabraut</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kóreskir chilivæng</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>1283.78</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>100267489</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Akrabraut</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi laxa nigiri 4 bita</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>1252.25</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>100234332</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Akrabraut</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri lax teriya</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>1243.24</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>100268874</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Akrabraut</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi soba núðlusalat me</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>1162.16</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>100271847</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Akrabraut</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi gyoza kjúklinga 6s</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1117.12</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>100267786</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Akrabraut</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi agúrku hosomaki 8b</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>720.72</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>100211702</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Akrabraut</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri vegan tófú</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>621.62</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>100270361</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Akranesi</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklinga katsu po</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>6432.4241</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>100261170</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Akranesi</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki soba núðlur m</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>3945.94</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>100266622</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Akranesi</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir so</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>3585.5854</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>100270217</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Akranesi</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi Poke Laxakadó hrís</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>2144.16</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>100261167</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Akranesi</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki udon núðlur m</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>1972.9729</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>100266623</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Akranesi</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri vegan tófú</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1864.86</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>100270361</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Akranesi</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri kjúklingas</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>1243.24</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>100268871</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Akranesi</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sterkur tú</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>621.62</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>100268875</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Austurveri</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri lax teriya</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>3729.72</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>100268874</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Austurveri</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir ch</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>3585.58</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>100270213</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Austurveri</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi vegan gyoza-ramen </t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>3225.23</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>100268873</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Austurveri</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi gyoza kjúklinga 6s</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>2234.2371</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>100267786</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Austurveri</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki soba núðlur m</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>1972.97</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>100266622</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Austurveri</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi grillaður kjúkling</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>1702.7</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>100268872</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Austurveri</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi rjóma-ramen með sv</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>1702.7</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>100268876</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Austurveri</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi edamame með sjávar</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>765.77</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>100267485</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Austurveri</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sterkur tú</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>621.62</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>100268875</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Borgartún</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki soba núðlur m</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>3945.9429</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>100266622</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Borgartún</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri lax teriya</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>3108.1</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>100268874</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Borgartún</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi vegan eldfjallarúl</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>2612.62</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>100234290</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Borgartún</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki udon núðlur m</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>1972.97</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>100266623</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Borgartún</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi laxafantasía 12bit</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>1963.95</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>100234285</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Borgartún</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sterkur tú</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>1864.86</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>100268875</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Borgartún</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir ch</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>1792.79</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>100270213</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Borgartún</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir so</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>1792.79</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>100270217</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Borgartún</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi soba núðlusalat me</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>1162.16</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>100271847</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Borgartún</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sulimi sal</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>621.62</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>100268877</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Bíldshöfða</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri lax teriya</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>14265.7416</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>100268874</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Bíldshöfða</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri kjúklingas</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>11590.0748</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>100268871</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Bíldshöfða</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi grillaður kjúkling</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>10216.2227</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>100268872</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Bíldshöfða</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi rjóma-ramen með sv</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>6810.8</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>100268876</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Bíldshöfða</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sterkur tú</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>5594.59</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>100268875</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Bíldshöfða</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi gyoza kjúklinga 6s</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>4468.4771</v>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>100267786</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Bíldshöfða</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi vegan gyoza-ramen </t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>3225.23</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>100268873</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Bíldshöfða</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sulimi sal</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>2454.96</v>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>100268877</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Bíldshöfða</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir so</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>1792.79</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>100270217</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Bíldshöfða</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi sojasósa</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>427.02</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G53" s="10" t="inlineStr">
+        <is>
+          <t>100208430</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Bíldshöfða</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi sterkt majó</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>136.94</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>100234273</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Fitjabraut</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi sushi lækkað verð </t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>7207.200000000001</v>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>100227278</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="17" customHeight="1">
+      <c r="A56" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Fitjabraut</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi rjóma-ramen með sv</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>5108.11</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>100268876</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="17" customHeight="1">
+      <c r="A57" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Fitjabraut</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi vegan gyoza-ramen </t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="n">
+        <v>4837.83</v>
+      </c>
+      <c r="F57" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>100268873</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Fitjabraut</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sterkur tú</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>3698.19</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>100268875</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Fitjabraut</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi soba núðlusalat me</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="n">
+        <v>3486.48</v>
+      </c>
+      <c r="F59" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>100271847</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Fitjabraut</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi rækju katsu karrí </t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>2423.43</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>100269266</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Fitjabraut</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi grillaður lax &amp; so</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="n">
+        <v>1972.98</v>
+      </c>
+      <c r="F61" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="10" t="inlineStr">
+        <is>
+          <t>100270215</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Fitjabraut</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri vegan tófú</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>1864.86</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>100270361</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Fitjabraut</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir so</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="n">
+        <v>1792.79</v>
+      </c>
+      <c r="F63" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
+        <is>
+          <t>100270217</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="17" customHeight="1">
+      <c r="A64" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Fitjabraut</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi laxatartar salat</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>1783.78</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>100208432</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="17" customHeight="1">
+      <c r="A65" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Fitjabraut</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi Rainbow maki 4bita</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="n">
+        <v>1441.44</v>
+      </c>
+      <c r="F65" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
+        <is>
+          <t>100246816</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="17" customHeight="1">
+      <c r="A66" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Fitjabraut</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sulimi sal</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>1243.24</v>
+      </c>
+      <c r="F66" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>100268877</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="17" customHeight="1">
+      <c r="A67" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Fitjabraut</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi wakame salat</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="n">
+        <v>1099.1</v>
+      </c>
+      <c r="F67" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>100208434</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="17" customHeight="1">
+      <c r="A68" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Fitjabraut</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi súrsað engifer</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>288.29</v>
+      </c>
+      <c r="F68" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>100270091</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Flatahrauni</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri lax teriya</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="n">
+        <v>17405.3832</v>
+      </c>
+      <c r="F69" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="G69" s="10" t="inlineStr">
+        <is>
+          <t>100268874</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Flatahrauni</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri kjúklingas</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>13022.4916</v>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>100268871</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="17" customHeight="1">
+      <c r="A71" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Flatahrauni</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sulimi sal</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="n">
+        <v>7459.44</v>
+      </c>
+      <c r="F71" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>100268877</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="17" customHeight="1">
+      <c r="A72" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Flatahrauni</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi vegan gyoza-ramen </t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>6450.4626</v>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>100268873</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="17" customHeight="1">
+      <c r="A73" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Flatahrauni</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki soba núðlur m</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="n">
+        <v>5918.93</v>
+      </c>
+      <c r="F73" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t>100266622</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="17" customHeight="1">
+      <c r="A74" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Flatahrauni</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sterkur tú</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>5563.05</v>
+      </c>
+      <c r="F74" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>100268875</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="17" customHeight="1">
+      <c r="A75" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Flatahrauni</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi grillaður lax &amp; so</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="n">
+        <v>3945.94</v>
+      </c>
+      <c r="F75" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>100270215</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="17" customHeight="1">
+      <c r="A76" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Flatahrauni</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi wakame salat</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>2747.75</v>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>100208434</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="17" customHeight="1">
+      <c r="A77" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Flatahrauni</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki udon núðlur m</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="n">
+        <v>1972.97</v>
+      </c>
+      <c r="F77" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="10" t="inlineStr">
+        <is>
+          <t>100266623</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="17" customHeight="1">
+      <c r="A78" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Flatahrauni</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir so</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>1792.79</v>
+      </c>
+      <c r="F78" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>100270217</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="17" customHeight="1">
+      <c r="A79" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Flatahrauni</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi rjóma-ramen með sv</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="n">
+        <v>1702.7</v>
+      </c>
+      <c r="F79" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="10" t="inlineStr">
+        <is>
+          <t>100268876</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="17" customHeight="1">
+      <c r="A80" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Flatahrauni</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi edamame með sjávar</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="n">
+        <v>1531.54</v>
+      </c>
+      <c r="F80" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>100267485</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="17" customHeight="1">
+      <c r="A81" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Flatahrauni</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi kóreskir vængir 6 </t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="n">
+        <v>1283.78</v>
+      </c>
+      <c r="F81" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="10" t="inlineStr">
+        <is>
+          <t>100267488</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="17" customHeight="1">
+      <c r="A82" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Flatahrauni</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi soba núðlusalat me</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="n">
+        <v>1162.17</v>
+      </c>
+      <c r="F82" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>100271847</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="17" customHeight="1">
+      <c r="A83" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Flatahrauni</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi gúrku sesam salat</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="n">
+        <v>621.62</v>
+      </c>
+      <c r="F83" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
+        <is>
+          <t>100270085</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="17" customHeight="1">
+      <c r="A84" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Flatahrauni</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi sojasósa</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="n">
+        <v>252.25</v>
+      </c>
+      <c r="F84" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>100208430</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="17" customHeight="1">
+      <c r="A85" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Flatahrauni</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yuzu majónes</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="n">
+        <v>144.14</v>
+      </c>
+      <c r="F85" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="10" t="inlineStr">
+        <is>
+          <t>100270087</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="17" customHeight="1">
+      <c r="A86" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Grafarholti</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki soba núðlur m</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="n">
+        <v>1972.97</v>
+      </c>
+      <c r="F86" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>100266622</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="17" customHeight="1">
+      <c r="A87" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Grafarholti</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingur &amp; sætnú</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="n">
+        <v>1972.97</v>
+      </c>
+      <c r="F87" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="10" t="inlineStr">
+        <is>
+          <t>100270212</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="17" customHeight="1">
+      <c r="A88" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Grafarholti</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi grillaður lax &amp; so</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="n">
+        <v>1972.97</v>
+      </c>
+      <c r="F88" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>100270215</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="17" customHeight="1">
+      <c r="A89" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Grafarholti</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir so</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="n">
+        <v>1792.79</v>
+      </c>
+      <c r="F89" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
+        <is>
+          <t>100270217</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="17" customHeight="1">
+      <c r="A90" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Grafarholti</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi laxa nigiri 4 bita</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="n">
+        <v>1252.25</v>
+      </c>
+      <c r="F90" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>100234332</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="17" customHeight="1">
+      <c r="A91" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Grafarholti</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sterkur tú</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="n">
+        <v>621.6215999999999</v>
+      </c>
+      <c r="F91" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="10" t="inlineStr">
+        <is>
+          <t>100268875</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="17" customHeight="1">
+      <c r="A92" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Grafarholti</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri kjúklingas</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v>621.62</v>
+      </c>
+      <c r="F92" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>100268871</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="17" customHeight="1">
+      <c r="A93" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Grafarholti</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri vegan tófú</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="n">
+        <v>621.62</v>
+      </c>
+      <c r="F93" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="10" t="inlineStr">
+        <is>
+          <t>100270361</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="17" customHeight="1">
+      <c r="A94" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Granda</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri lax teriya</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="n">
+        <v>17373.8432</v>
+      </c>
+      <c r="F94" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>100268874</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="17" customHeight="1">
+      <c r="A95" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Granda</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sterkur tú</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="n">
+        <v>14887.3564</v>
+      </c>
+      <c r="F95" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
+        <is>
+          <t>100268875</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="17" customHeight="1">
+      <c r="A96" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Granda</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri kjúklingas</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="n">
+        <v>14234.2032</v>
+      </c>
+      <c r="F96" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>100268871</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="17" customHeight="1">
+      <c r="A97" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Granda</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sulimi sal</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v>6837.82</v>
+      </c>
+      <c r="F97" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="G97" s="10" t="inlineStr">
+        <is>
+          <t>100268877</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="17" customHeight="1">
+      <c r="A98" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Granda</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki soba núðlur m</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="n">
+        <v>5918.91</v>
+      </c>
+      <c r="F98" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>100266622</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="17" customHeight="1">
+      <c r="A99" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Granda</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki udon núðlur m</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>3945.94</v>
+      </c>
+      <c r="F99" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G99" s="10" t="inlineStr">
+        <is>
+          <t>100266623</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="17" customHeight="1">
+      <c r="A100" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Granda</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir ch</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="n">
+        <v>1792.79</v>
+      </c>
+      <c r="F100" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>100270213</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="17" customHeight="1">
+      <c r="A101" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Granda</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kóreskir chilivæng</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="n">
+        <v>1283.78</v>
+      </c>
+      <c r="F101" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="10" t="inlineStr">
+        <is>
+          <t>100267489</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="17" customHeight="1">
+      <c r="A102" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Granda</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi sterkt majó</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="n">
+        <v>1009.01</v>
+      </c>
+      <c r="F102" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>100234273</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="17" customHeight="1">
+      <c r="A103" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Granda</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri vegan tófú</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="n">
+        <v>621.62</v>
+      </c>
+      <c r="F103" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="10" t="inlineStr">
+        <is>
+          <t>100270361</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="17" customHeight="1">
+      <c r="A104" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Granda</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi sojasósa</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="n">
+        <v>126.12</v>
+      </c>
+      <c r="F104" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>100208430</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="17" customHeight="1">
+      <c r="A105" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Hallveigarstíg</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi 11 Ekkert hrátt 14</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v>5243.24</v>
+      </c>
+      <c r="F105" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G105" s="10" t="inlineStr">
+        <is>
+          <t>100256707</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="17" customHeight="1">
+      <c r="A106" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Hallveigarstíg</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklinga katsu po</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="n">
+        <v>4288.28</v>
+      </c>
+      <c r="F106" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>100261170</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="17" customHeight="1">
+      <c r="A107" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Hallveigarstíg</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki udon núðlur m</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="n">
+        <v>3945.94</v>
+      </c>
+      <c r="F107" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G107" s="10" t="inlineStr">
+        <is>
+          <t>100266623</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="17" customHeight="1">
+      <c r="A108" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Hallveigarstíg</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi Laxatrío 16bitar</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="n">
+        <v>3351.35</v>
+      </c>
+      <c r="F108" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>100246846</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="17" customHeight="1">
+      <c r="A109" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Hallveigarstíg</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi 13 Allt það besta </t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="n">
+        <v>3126.13</v>
+      </c>
+      <c r="F109" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="10" t="inlineStr">
+        <is>
+          <t>100256723</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="17" customHeight="1">
+      <c r="A110" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Hallveigarstíg</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi kóreskir vængir 6 </t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="n">
+        <v>2567.56</v>
+      </c>
+      <c r="F110" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>100267488</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="17" customHeight="1">
+      <c r="A111" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Hallveigarstíg</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kóreskir chilivæng</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="n">
+        <v>2567.56</v>
+      </c>
+      <c r="F111" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G111" s="10" t="inlineStr">
+        <is>
+          <t>100267489</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="17" customHeight="1">
+      <c r="A112" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Hallveigarstíg</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi Poke veganbliss hr</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="n">
+        <v>2144.14</v>
+      </c>
+      <c r="F112" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>100261171</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="17" customHeight="1">
+      <c r="A113" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Hallveigarstíg</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi eldfjallarúlla 6bi</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v>1909.91</v>
+      </c>
+      <c r="F113" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="10" t="inlineStr">
+        <is>
+          <t>100220462</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="17" customHeight="1">
+      <c r="A114" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Hallveigarstíg</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingakatsu 8bi</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="n">
+        <v>1783.78</v>
+      </c>
+      <c r="F114" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>100211697</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="17" customHeight="1">
+      <c r="A115" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B115" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Hallveigarstíg</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sterkur tú</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v>621.62</v>
+      </c>
+      <c r="F115" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="10" t="inlineStr">
+        <is>
+          <t>100268875</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="17" customHeight="1">
+      <c r="A116" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Jafnaseli</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklinga katsu po</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="n">
+        <v>6325.23</v>
+      </c>
+      <c r="F116" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>100261170</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="17" customHeight="1">
+      <c r="A117" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B117" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Jafnaseli</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi laxafantasía 12bit</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v>5891.89</v>
+      </c>
+      <c r="F117" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G117" s="10" t="inlineStr">
+        <is>
+          <t>100234285</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="17" customHeight="1">
+      <c r="A118" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Jafnaseli</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingakatsu 8bi</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="n">
+        <v>3567.56</v>
+      </c>
+      <c r="F118" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>100211697</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="17" customHeight="1">
+      <c r="A119" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Jafnaseli</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki udon núðlur m</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="n">
+        <v>1972.97</v>
+      </c>
+      <c r="F119" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="10" t="inlineStr">
+        <is>
+          <t>100266623</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="17" customHeight="1">
+      <c r="A120" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Lindum</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri lax teriya</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="n">
+        <v>18026.9816</v>
+      </c>
+      <c r="F120" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>100268874</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="17" customHeight="1">
+      <c r="A121" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Lindum</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri kjúklingas</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="n">
+        <v>13675.6448</v>
+      </c>
+      <c r="F121" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="G121" s="10" t="inlineStr">
+        <is>
+          <t>100268871</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="17" customHeight="1">
+      <c r="A122" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Lindum</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sterkur tú</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="n">
+        <v>11189.1732</v>
+      </c>
+      <c r="F122" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>100268875</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="17" customHeight="1">
+      <c r="A123" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Lindum</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sulimi sal</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="n">
+        <v>7459.44</v>
+      </c>
+      <c r="F123" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="G123" s="10" t="inlineStr">
+        <is>
+          <t>100268877</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="17" customHeight="1">
+      <c r="A124" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Lindum</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki udon núðlur m</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="n">
+        <v>5918.91</v>
+      </c>
+      <c r="F124" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>100266623</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="17" customHeight="1">
+      <c r="A125" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Lindum</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi sushi lækkað verð </t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="n">
+        <v>3738.74</v>
+      </c>
+      <c r="F125" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G125" s="10" t="inlineStr">
+        <is>
+          <t>100227280</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="17" customHeight="1">
+      <c r="A126" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Lindum</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir ch</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="n">
+        <v>3585.58</v>
+      </c>
+      <c r="F126" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>100270213</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="17" customHeight="1">
+      <c r="A127" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Lindum</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingur &amp; sætnú</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="n">
+        <v>1972.97</v>
+      </c>
+      <c r="F127" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="10" t="inlineStr">
+        <is>
+          <t>100270212</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="17" customHeight="1">
+      <c r="A128" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Lindum</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi wakame salat</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="n">
+        <v>549.55</v>
+      </c>
+      <c r="F128" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>100208434</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="17" customHeight="1">
+      <c r="A129" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Lindum</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi sojasósa</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="n">
+        <v>315.313</v>
+      </c>
+      <c r="F129" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G129" s="10" t="inlineStr">
+        <is>
+          <t>100208430</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="17" customHeight="1">
+      <c r="A130" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Mosfellsbæ</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri kjúklingas</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="n">
+        <v>11810.7916</v>
+      </c>
+      <c r="F130" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>100268871</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="17" customHeight="1">
+      <c r="A131" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B131" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Mosfellsbæ</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sterkur tú</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="n">
+        <v>9945.9216</v>
+      </c>
+      <c r="F131" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="G131" s="10" t="inlineStr">
+        <is>
+          <t>100268875</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="17" customHeight="1">
+      <c r="A132" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Mosfellsbæ</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri lax teriya</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="n">
+        <v>9292.780000000001</v>
+      </c>
+      <c r="F132" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>100268874</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="17" customHeight="1">
+      <c r="A133" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B133" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Mosfellsbæ</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi gyoza kjúklinga 6s</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="n">
+        <v>6702.7</v>
+      </c>
+      <c r="F133" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G133" s="10" t="inlineStr">
+        <is>
+          <t>100267786</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="17" customHeight="1">
+      <c r="A134" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Mosfellsbæ</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sulimi sal</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="n">
+        <v>5594.58</v>
+      </c>
+      <c r="F134" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>100268877</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="17" customHeight="1">
+      <c r="A135" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B135" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Mosfellsbæ</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi rjóma-ramen með sv</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="n">
+        <v>3405.4</v>
+      </c>
+      <c r="F135" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G135" s="10" t="inlineStr">
+        <is>
+          <t>100268876</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="17" customHeight="1">
+      <c r="A136" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Mosfellsbæ</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi vegan gyoza-ramen </t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="n">
+        <v>3225.23</v>
+      </c>
+      <c r="F136" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>100268873</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="17" customHeight="1">
+      <c r="A137" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B137" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Mosfellsbæ</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir ch</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="n">
+        <v>1792.79</v>
+      </c>
+      <c r="F137" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="10" t="inlineStr">
+        <is>
+          <t>100270213</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="17" customHeight="1">
+      <c r="A138" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Mosfellsbæ</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi sushi lækkað verð </t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="n">
+        <v>1171.17</v>
+      </c>
+      <c r="F138" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>100227278</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="17" customHeight="1">
+      <c r="A139" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B139" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Mosfellsbæ</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi soba núðlusalat me</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="n">
+        <v>1162.16</v>
+      </c>
+      <c r="F139" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" s="10" t="inlineStr">
+        <is>
+          <t>100271847</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="17" customHeight="1">
+      <c r="A140" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Mosfellsbæ</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi 38 Avókadó hosomak</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="n">
+        <v>873.88</v>
+      </c>
+      <c r="F140" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>100256727</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="17" customHeight="1">
+      <c r="A141" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B141" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C141" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Mosfellsbæ</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi mangó hosomaki 8bi</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="n">
+        <v>837.84</v>
+      </c>
+      <c r="F141" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" s="10" t="inlineStr">
+        <is>
+          <t>100234295</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="17" customHeight="1">
+      <c r="A142" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Mosfellsbæ</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi sterkt majó</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="n">
+        <v>288.28</v>
+      </c>
+      <c r="F142" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>100234273</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="17" customHeight="1">
+      <c r="A143" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B143" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C143" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Mosfellsbæ</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi sojasósa</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="n">
+        <v>252.24</v>
+      </c>
+      <c r="F143" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G143" s="10" t="inlineStr">
+        <is>
+          <t>100208430</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="17" customHeight="1">
+      <c r="A144" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Mosfellsbæ</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi unagi sósa</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="n">
+        <v>144.14</v>
+      </c>
+      <c r="F144" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>100270088</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="17" customHeight="1">
+      <c r="A145" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B145" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Mosfellsbæ</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi súrsað engifer</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="n">
+        <v>144.14</v>
+      </c>
+      <c r="F145" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="10" t="inlineStr">
+        <is>
+          <t>100270091</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="17" customHeight="1">
+      <c r="A146" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Norðurhellu</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingur &amp; sætnú</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="n">
+        <v>3945.95</v>
+      </c>
+      <c r="F146" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>100270212</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="17" customHeight="1">
+      <c r="A147" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B147" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Norðurhellu</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi gyoza kjúklinga 6s</t>
+        </is>
+      </c>
+      <c r="E147" s="12" t="n">
+        <v>2144.14</v>
+      </c>
+      <c r="F147" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G147" s="10" t="inlineStr">
+        <is>
+          <t>100266621</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="17" customHeight="1">
+      <c r="A148" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Norðurhellu</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki soba núðlur m</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="n">
+        <v>1972.97</v>
+      </c>
+      <c r="F148" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>100266622</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="17" customHeight="1">
+      <c r="A149" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B149" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C149" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Norðurhellu</t>
+        </is>
+      </c>
+      <c r="D149" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki udon núðlur m</t>
+        </is>
+      </c>
+      <c r="E149" s="12" t="n">
+        <v>1972.97</v>
+      </c>
+      <c r="F149" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" s="10" t="inlineStr">
+        <is>
+          <t>100266623</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="17" customHeight="1">
+      <c r="A150" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Norðurhellu</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi 6. Smakk af því be</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="n">
+        <v>1927.93</v>
+      </c>
+      <c r="F150" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>100256732</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="17" customHeight="1">
+      <c r="A151" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B151" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C151" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Norðurhellu</t>
+        </is>
+      </c>
+      <c r="D151" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi eldfjallarúlla 6bi</t>
+        </is>
+      </c>
+      <c r="E151" s="12" t="n">
+        <v>1909.91</v>
+      </c>
+      <c r="F151" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="10" t="inlineStr">
+        <is>
+          <t>100220462</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="17" customHeight="1">
+      <c r="A152" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Norðurhellu</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir ch</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="n">
+        <v>1792.79</v>
+      </c>
+      <c r="F152" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>100270213</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="17" customHeight="1">
+      <c r="A153" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B153" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C153" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Norðurhellu</t>
+        </is>
+      </c>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir so</t>
+        </is>
+      </c>
+      <c r="E153" s="12" t="n">
+        <v>1792.79</v>
+      </c>
+      <c r="F153" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" s="10" t="inlineStr">
+        <is>
+          <t>100270217</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="17" customHeight="1">
+      <c r="A154" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Norðurhellu</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingakatsu 8bi</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="n">
+        <v>1783.78</v>
+      </c>
+      <c r="F154" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>100211697</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="17" customHeight="1">
+      <c r="A155" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B155" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C155" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Norðurhellu</t>
+        </is>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi vegan gyoza-ramen </t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="n">
+        <v>1612.61</v>
+      </c>
+      <c r="F155" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="10" t="inlineStr">
+        <is>
+          <t>100268873</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="17" customHeight="1">
+      <c r="A156" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Norðurhellu</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi soba núðlusalat me</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="n">
+        <v>1162.16</v>
+      </c>
+      <c r="F156" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>100271847</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="17" customHeight="1">
+      <c r="A157" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B157" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C157" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Norðurhellu</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sterkur tú</t>
+        </is>
+      </c>
+      <c r="E157" s="12" t="n">
+        <v>621.62</v>
+      </c>
+      <c r="F157" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" s="10" t="inlineStr">
+        <is>
+          <t>100268875</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="17" customHeight="1">
+      <c r="A158" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Selfossi</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi vegan gyoza-ramen </t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="n">
+        <v>4837.83</v>
+      </c>
+      <c r="F158" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>100268873</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="17" customHeight="1">
+      <c r="A159" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B159" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C159" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Selfossi</t>
+        </is>
+      </c>
+      <c r="D159" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi rjóma-ramen með sv</t>
+        </is>
+      </c>
+      <c r="E159" s="12" t="n">
+        <v>3405.4</v>
+      </c>
+      <c r="F159" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G159" s="10" t="inlineStr">
+        <is>
+          <t>100268876</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="17" customHeight="1">
+      <c r="A160" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Selfossi</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir so</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="n">
+        <v>1792.79</v>
+      </c>
+      <c r="F160" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>100270217</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="17" customHeight="1">
+      <c r="A161" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B161" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C161" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Selfossi</t>
+        </is>
+      </c>
+      <c r="D161" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi kóreskir vængir 6 </t>
+        </is>
+      </c>
+      <c r="E161" s="12" t="n">
+        <v>1283.79</v>
+      </c>
+      <c r="F161" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" s="10" t="inlineStr">
+        <is>
+          <t>100267488</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="17" customHeight="1">
+      <c r="A162" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Selfossi</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kóreskir chilivæng</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="n">
+        <v>1283.77</v>
+      </c>
+      <c r="F162" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>100267489</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="17" customHeight="1">
+      <c r="A163" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B163" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C163" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Selfossi</t>
+        </is>
+      </c>
+      <c r="D163" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi laxatartar salat</t>
+        </is>
+      </c>
+      <c r="E163" s="12" t="n">
+        <v>891.89</v>
+      </c>
+      <c r="F163" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" s="10" t="inlineStr">
+        <is>
+          <t>100208432</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="17" customHeight="1">
+      <c r="A164" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri lax teriya</t>
+        </is>
+      </c>
+      <c r="E164" s="6" t="n">
+        <v>12990.9732</v>
+      </c>
+      <c r="F164" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>100268874</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="17" customHeight="1">
+      <c r="A165" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B165" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C165" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D165" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri kjúklingas</t>
+        </is>
+      </c>
+      <c r="E165" s="12" t="n">
+        <v>12990.9665</v>
+      </c>
+      <c r="F165" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="G165" s="10" t="inlineStr">
+        <is>
+          <t>100268871</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="17" customHeight="1">
+      <c r="A166" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sterkur tú</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="n">
+        <v>10472.95</v>
+      </c>
+      <c r="F166" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>100268875</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="17" customHeight="1">
+      <c r="A167" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B167" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C167" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D167" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sulimi sal</t>
+        </is>
+      </c>
+      <c r="E167" s="12" t="n">
+        <v>7396.3801</v>
+      </c>
+      <c r="F167" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="G167" s="10" t="inlineStr">
+        <is>
+          <t>100268877</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="17" customHeight="1">
+      <c r="A168" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi rjóma-ramen með sv</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="n">
+        <v>5108.1</v>
+      </c>
+      <c r="F168" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>100268876</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="17" customHeight="1">
+      <c r="A169" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B169" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C169" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D169" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi vegan gyoza-ramen </t>
+        </is>
+      </c>
+      <c r="E169" s="12" t="n">
+        <v>4837.83</v>
+      </c>
+      <c r="F169" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G169" s="10" t="inlineStr">
+        <is>
+          <t>100268873</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="17" customHeight="1">
+      <c r="A170" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi sushi lækkað verð </t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="n">
+        <v>3963.97</v>
+      </c>
+      <c r="F170" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>100227279</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="17" customHeight="1">
+      <c r="A171" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B171" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C171" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D171" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki udon núðlur m</t>
+        </is>
+      </c>
+      <c r="E171" s="12" t="n">
+        <v>3945.95</v>
+      </c>
+      <c r="F171" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G171" s="10" t="inlineStr">
+        <is>
+          <t>100266623</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="17" customHeight="1">
+      <c r="A172" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki soba núðlur m</t>
+        </is>
+      </c>
+      <c r="E172" s="6" t="n">
+        <v>1972.97</v>
+      </c>
+      <c r="F172" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" s="4" t="inlineStr">
+        <is>
+          <t>100266622</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="17" customHeight="1">
+      <c r="A173" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B173" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C173" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D173" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi grillaður lax &amp; so</t>
+        </is>
+      </c>
+      <c r="E173" s="12" t="n">
+        <v>1972.97</v>
+      </c>
+      <c r="F173" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G173" s="10" t="inlineStr">
+        <is>
+          <t>100270215</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="17" customHeight="1">
+      <c r="A174" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklingavængir ch</t>
+        </is>
+      </c>
+      <c r="E174" s="6" t="n">
+        <v>1792.79</v>
+      </c>
+      <c r="F174" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t>100270213</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="17" customHeight="1">
+      <c r="A175" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B175" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C175" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D175" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi kóreskir vængir 6 </t>
+        </is>
+      </c>
+      <c r="E175" s="12" t="n">
+        <v>1283.78</v>
+      </c>
+      <c r="F175" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" s="10" t="inlineStr">
+        <is>
+          <t>100267488</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="17" customHeight="1">
+      <c r="A176" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi soba núðlusalat me</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="n">
+        <v>1162.16</v>
+      </c>
+      <c r="F176" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>100271847</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="17" customHeight="1">
+      <c r="A177" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B177" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C177" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D177" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi gyoza kjúklinga 6s</t>
+        </is>
+      </c>
+      <c r="E177" s="12" t="n">
+        <v>1117.12</v>
+      </c>
+      <c r="F177" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" s="10" t="inlineStr">
+        <is>
+          <t>100267786</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="17" customHeight="1">
+      <c r="A178" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi gúrku sesam salat</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="n">
+        <v>621.62</v>
+      </c>
+      <c r="F178" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>100270085</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="17" customHeight="1">
+      <c r="A179" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B179" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C179" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D179" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri vegan tófú</t>
+        </is>
+      </c>
+      <c r="E179" s="12" t="n">
+        <v>621.62</v>
+      </c>
+      <c r="F179" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" s="10" t="inlineStr">
+        <is>
+          <t>100270361</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="17" customHeight="1">
+      <c r="A180" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D180" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi wakame salat</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="n">
+        <v>549.55</v>
+      </c>
+      <c r="F180" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>100208434</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="17" customHeight="1">
+      <c r="A181" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B181" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C181" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D181" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi sojasósa</t>
+        </is>
+      </c>
+      <c r="E181" s="12" t="n">
+        <v>252.243</v>
+      </c>
+      <c r="F181" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G181" s="10" t="inlineStr">
+        <is>
+          <t>100208430</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="17" customHeight="1">
+      <c r="A182" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Skeifan 19</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi súrsað engifer</t>
+        </is>
+      </c>
+      <c r="E182" s="6" t="n">
+        <v>144.14</v>
+      </c>
+      <c r="F182" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>100270091</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="17" customHeight="1">
+      <c r="A183" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B183" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C183" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Vallakór</t>
+        </is>
+      </c>
+      <c r="D183" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi Lítið laxatrío 10b</t>
+        </is>
+      </c>
+      <c r="E183" s="12" t="n">
+        <v>3927.92</v>
+      </c>
+      <c r="F183" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G183" s="10" t="inlineStr">
+        <is>
+          <t>100246849</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="17" customHeight="1">
+      <c r="A184" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Vallakór</t>
+        </is>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi laxafantasía 12bit</t>
+        </is>
+      </c>
+      <c r="E184" s="6" t="n">
+        <v>3927.9139</v>
+      </c>
+      <c r="F184" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G184" s="4" t="inlineStr">
+        <is>
+          <t>100234285</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="17" customHeight="1">
+      <c r="A185" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B185" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C185" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Vallakór</t>
+        </is>
+      </c>
+      <c r="D185" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi 13 Allt það besta </t>
+        </is>
+      </c>
+      <c r="E185" s="12" t="n">
+        <v>3126.13</v>
+      </c>
+      <c r="F185" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G185" s="10" t="inlineStr">
+        <is>
+          <t>100256723</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="17" customHeight="1">
+      <c r="A186" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Vallakór</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi kóreskir vængir 6 </t>
+        </is>
+      </c>
+      <c r="E186" s="6" t="n">
+        <v>2567.56</v>
+      </c>
+      <c r="F186" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>100267488</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="17" customHeight="1">
+      <c r="A187" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B187" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C187" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Vallakór</t>
+        </is>
+      </c>
+      <c r="D187" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kóreskir chilivæng</t>
+        </is>
+      </c>
+      <c r="E187" s="12" t="n">
+        <v>2567.55</v>
+      </c>
+      <c r="F187" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G187" s="10" t="inlineStr">
+        <is>
+          <t>100267489</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="17" customHeight="1">
+      <c r="A188" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Vallakór</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sulimi sal</t>
+        </is>
+      </c>
+      <c r="E188" s="6" t="n">
+        <v>2486.48</v>
+      </c>
+      <c r="F188" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G188" s="4" t="inlineStr">
+        <is>
+          <t>100268877</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="17" customHeight="1">
+      <c r="A189" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B189" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C189" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Vallakór</t>
+        </is>
+      </c>
+      <c r="D189" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi kjúklinga katsu po</t>
+        </is>
+      </c>
+      <c r="E189" s="12" t="n">
+        <v>2144.1441</v>
+      </c>
+      <c r="F189" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" s="10" t="inlineStr">
+        <is>
+          <t>100261170</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="17" customHeight="1">
+      <c r="A190" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Vallakór</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi yaki soba núðlur m</t>
+        </is>
+      </c>
+      <c r="E190" s="6" t="n">
+        <v>1972.97</v>
+      </c>
+      <c r="F190" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" s="4" t="inlineStr">
+        <is>
+          <t>100266622</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="17" customHeight="1">
+      <c r="A191" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B191" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C191" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Vallakór</t>
+        </is>
+      </c>
+      <c r="D191" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi eldfjallarúlla 6bi</t>
+        </is>
+      </c>
+      <c r="E191" s="12" t="n">
+        <v>1909.9099</v>
+      </c>
+      <c r="F191" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" s="10" t="inlineStr">
+        <is>
+          <t>100220462</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="17" customHeight="1">
+      <c r="A192" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Vallakór</t>
+        </is>
+      </c>
+      <c r="D192" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri kjúklingas</t>
+        </is>
+      </c>
+      <c r="E192" s="6" t="n">
+        <v>1864.8616</v>
+      </c>
+      <c r="F192" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>100268871</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="17" customHeight="1">
+      <c r="A193" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B193" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C193" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Vallakór</t>
+        </is>
+      </c>
+      <c r="D193" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tokyo Sushi laxa og epla maki </t>
+        </is>
+      </c>
+      <c r="E193" s="12" t="n">
+        <v>1738.74</v>
+      </c>
+      <c r="F193" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" s="10" t="inlineStr">
+        <is>
+          <t>100234308</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="17" customHeight="1">
+      <c r="A194" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Vallakór</t>
+        </is>
+      </c>
+      <c r="D194" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi grillaður kjúkling</t>
+        </is>
+      </c>
+      <c r="E194" s="6" t="n">
+        <v>1702.7</v>
+      </c>
+      <c r="F194" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" s="4" t="inlineStr">
+        <is>
+          <t>100268872</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="17" customHeight="1">
+      <c r="A195" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B195" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C195" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Vallakór</t>
+        </is>
+      </c>
+      <c r="D195" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi vegan eldfjallarúl</t>
+        </is>
+      </c>
+      <c r="E195" s="12" t="n">
+        <v>1306.31</v>
+      </c>
+      <c r="F195" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" s="10" t="inlineStr">
+        <is>
+          <t>100234290</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="17" customHeight="1">
+      <c r="A196" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Vallakór</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi laxa nigiri 4 bita</t>
+        </is>
+      </c>
+      <c r="E196" s="6" t="n">
+        <v>1252.25</v>
+      </c>
+      <c r="F196" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" s="4" t="inlineStr">
+        <is>
+          <t>100234332</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="17" customHeight="1">
+      <c r="A197" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B197" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C197" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Vallakór</t>
+        </is>
+      </c>
+      <c r="D197" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri sterkur tú</t>
+        </is>
+      </c>
+      <c r="E197" s="12" t="n">
+        <v>1243.2416</v>
+      </c>
+      <c r="F197" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G197" s="10" t="inlineStr">
+        <is>
+          <t>100268875</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="17" customHeight="1">
+      <c r="A198" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Vallakór</t>
+        </is>
+      </c>
+      <c r="D198" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri lax teriya</t>
+        </is>
+      </c>
+      <c r="E198" s="6" t="n">
+        <v>1243.24</v>
+      </c>
+      <c r="F198" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G198" s="4" t="inlineStr">
+        <is>
+          <t>100268874</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="17" customHeight="1">
+      <c r="A199" s="9" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B199" s="10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C199" s="11" t="inlineStr">
+        <is>
+          <t>Krónan Vallakór</t>
+        </is>
+      </c>
+      <c r="D199" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi onigiri vegan tófú</t>
+        </is>
+      </c>
+      <c r="E199" s="12" t="n">
+        <v>590.09</v>
+      </c>
+      <c r="F199" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" s="10" t="inlineStr">
+        <is>
+          <t>100270361</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="17" customHeight="1">
+      <c r="A200" s="3" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C200" s="5" t="inlineStr">
+        <is>
+          <t>Krónan Árbæ</t>
+        </is>
+      </c>
+      <c r="D200" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo Sushi 11 Ekkert hrátt 14</t>
+        </is>
+      </c>
+      <c r="E200" s="6" t="n">
+        <v>2621.62</v>
+      </c>
+      <c r="F200" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" s="4" t="inlineStr">
+        <is>
+          <t>100256707</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
